--- a/output/results.xlsx
+++ b/output/results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +47,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,9 +86,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -434,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -471,6 +505,87 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>गर्दन की नसों में दर्द का इलाज</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>मोटापा कम करने का तरीका</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>circumcision complications</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
